--- a/src/assets/data/sample-data-55emp-6proj.xlsx
+++ b/src/assets/data/sample-data-55emp-6proj.xlsx
@@ -2283,7 +2283,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
         <v>26</v>
@@ -2303,7 +2303,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -2323,7 +2323,7 @@
         <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
@@ -2343,7 +2343,7 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
@@ -2363,7 +2363,7 @@
         <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -2383,7 +2383,7 @@
         <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
         <v>43</v>
@@ -2403,7 +2403,7 @@
         <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
         <v>47</v>
@@ -2423,7 +2423,7 @@
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
         <v>51</v>
@@ -3313,7 +3313,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="H4:H12 G13:H56 A2:A12 D7:D12 A13:D56 G2:H3 D2:D3 A1:H1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D2:D3 G2:H3 A13:D56 D7:D12 A2:A12 G13:H56 H4:H12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/assets/data/sample-data-55emp-6proj.xlsx
+++ b/src/assets/data/sample-data-55emp-6proj.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885"/>
+    <workbookView windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="Nhân sự" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="346">
   <si>
     <t>ID</t>
   </si>
@@ -144,9 +144,6 @@
     <t>Ngô Tấn Lộc</t>
   </si>
   <si>
-    <t>Vận hành</t>
-  </si>
-  <si>
     <t>21/12/2020</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
     <t>Trần Văn Hậu</t>
   </si>
   <si>
-    <t>Kinh doanh</t>
-  </si>
-  <si>
     <t>27/10/2021</t>
   </si>
   <si>
@@ -168,9 +162,6 @@
     <t>Nguyễn Huỳnh Đông Triều</t>
   </si>
   <si>
-    <t>Marketing</t>
-  </si>
-  <si>
     <t>22/05/2019</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>Nguyễn Thanh Tú</t>
   </si>
   <si>
-    <t>Tài chính</t>
-  </si>
-  <si>
     <t>13/08/2020</t>
   </si>
   <si>
@@ -192,10 +180,7 @@
     <t>Hồ Đức Nam</t>
   </si>
   <si>
-    <t>Trưởng phòng Pháp lý</t>
-  </si>
-  <si>
-    <t>Pháp lý</t>
+    <t>Thực tập</t>
   </si>
   <si>
     <t>29/11/2017</t>
@@ -207,12 +192,6 @@
     <t>Ngô Minh Ngân</t>
   </si>
   <si>
-    <t>Trưởng phòng Nhân sự</t>
-  </si>
-  <si>
-    <t>Nhân sự</t>
-  </si>
-  <si>
     <t>26/10/2015</t>
   </si>
   <si>
@@ -222,12 +201,6 @@
     <t>Dương Quốc Nhung</t>
   </si>
   <si>
-    <t>Trưởng phòng Đào tạo</t>
-  </si>
-  <si>
-    <t>Đào tạo</t>
-  </si>
-  <si>
     <t>10/05/2017</t>
   </si>
   <si>
@@ -237,9 +210,6 @@
     <t>Nguyễn Hữu Phúc</t>
   </si>
   <si>
-    <t>Senior Backend Developer</t>
-  </si>
-  <si>
     <t>10/12/2020</t>
   </si>
   <si>
@@ -258,9 +228,6 @@
     <t>Lê Bảo Sơn</t>
   </si>
   <si>
-    <t>Senior Frontend Developer</t>
-  </si>
-  <si>
     <t>14/10/2018</t>
   </si>
   <si>
@@ -270,9 +237,6 @@
     <t>Phạm Xuân Thắng</t>
   </si>
   <si>
-    <t>Senior UI/UX Designer</t>
-  </si>
-  <si>
     <t>21/09/2024</t>
   </si>
   <si>
@@ -282,9 +246,6 @@
     <t>Hoàng Thu Thảo</t>
   </si>
   <si>
-    <t>Senior DevOps Engineer</t>
-  </si>
-  <si>
     <t>15/12/2016</t>
   </si>
   <si>
@@ -294,9 +255,6 @@
     <t>Huỳnh Văn Thịnh</t>
   </si>
   <si>
-    <t>Senior Sales Executive</t>
-  </si>
-  <si>
     <t>01/09/2024</t>
   </si>
   <si>
@@ -306,9 +264,6 @@
     <t>Phan Thị Thu</t>
   </si>
   <si>
-    <t>Senior Account Manager</t>
-  </si>
-  <si>
     <t>25/08/2017</t>
   </si>
   <si>
@@ -318,9 +273,6 @@
     <t>Vũ Đức Trang</t>
   </si>
   <si>
-    <t>Senior Marketing Specialist</t>
-  </si>
-  <si>
     <t>08/06/2015</t>
   </si>
   <si>
@@ -330,9 +282,6 @@
     <t>Võ Minh Trung</t>
   </si>
   <si>
-    <t>Senior Content Creator</t>
-  </si>
-  <si>
     <t>15/07/2016</t>
   </si>
   <si>
@@ -342,9 +291,6 @@
     <t>Đặng Quốc Tuấn</t>
   </si>
   <si>
-    <t>Kế toán trưởng</t>
-  </si>
-  <si>
     <t>13/01/2021</t>
   </si>
   <si>
@@ -354,9 +300,6 @@
     <t>Bùi Hữu Tùng</t>
   </si>
   <si>
-    <t>Senior Legal Counsel</t>
-  </si>
-  <si>
     <t>02/02/2023</t>
   </si>
   <si>
@@ -366,9 +309,6 @@
     <t>Đỗ Thành Vy</t>
   </si>
   <si>
-    <t>Senior HR Specialist</t>
-  </si>
-  <si>
     <t>27/06/2019</t>
   </si>
   <si>
@@ -378,9 +318,6 @@
     <t>Hồ Bảo Yến</t>
   </si>
   <si>
-    <t>Senior Trainer</t>
-  </si>
-  <si>
     <t>26/08/2023</t>
   </si>
   <si>
@@ -390,9 +327,6 @@
     <t>Ngô Xuân An</t>
   </si>
   <si>
-    <t>Backend Developer</t>
-  </si>
-  <si>
     <t>27/04/2018</t>
   </si>
   <si>
@@ -429,9 +363,6 @@
     <t>Lê Đức Hà</t>
   </si>
   <si>
-    <t>Frontend Developer</t>
-  </si>
-  <si>
     <t>19/11/2019</t>
   </si>
   <si>
@@ -450,9 +381,6 @@
     <t>Hoàng Quốc Hùng</t>
   </si>
   <si>
-    <t>UI/UX Designer</t>
-  </si>
-  <si>
     <t>17/10/2023</t>
   </si>
   <si>
@@ -471,9 +399,6 @@
     <t>Phan Thành Lan</t>
   </si>
   <si>
-    <t>DevOps Engineer</t>
-  </si>
-  <si>
     <t>16/08/2024</t>
   </si>
   <si>
@@ -492,9 +417,6 @@
     <t>Võ Xuân Long</t>
   </si>
   <si>
-    <t>Sales Executive</t>
-  </si>
-  <si>
     <t>09/01/2023</t>
   </si>
   <si>
@@ -522,9 +444,6 @@
     <t>Đỗ Thị Ngân</t>
   </si>
   <si>
-    <t>Account Manager</t>
-  </si>
-  <si>
     <t>07/05/2020</t>
   </si>
   <si>
@@ -543,9 +462,6 @@
     <t>Ngô Minh Phúc</t>
   </si>
   <si>
-    <t>Marketing Specialist</t>
-  </si>
-  <si>
     <t>16/07/2024</t>
   </si>
   <si>
@@ -573,9 +489,6 @@
     <t>Trần Thành Thắng</t>
   </si>
   <si>
-    <t>Content Creator</t>
-  </si>
-  <si>
     <t>01/03/2024</t>
   </si>
   <si>
@@ -594,9 +507,6 @@
     <t>Phạm Xuân Thịnh</t>
   </si>
   <si>
-    <t>Kế toán</t>
-  </si>
-  <si>
     <t>25/05/2019</t>
   </si>
   <si>
@@ -612,9 +522,6 @@
     <t>Huỳnh Văn Trang</t>
   </si>
   <si>
-    <t>Legal Associate</t>
-  </si>
-  <si>
     <t>22/03/2021</t>
   </si>
   <si>
@@ -633,9 +540,6 @@
     <t>Vũ Đức Tuấn</t>
   </si>
   <si>
-    <t>HR Specialist</t>
-  </si>
-  <si>
     <t>28/01/2015</t>
   </si>
   <si>
@@ -652,9 +556,6 @@
   </si>
   <si>
     <t>Đặng Quốc Vy</t>
-  </si>
-  <si>
-    <t>Trainer</t>
   </si>
   <si>
     <t>21/01/2019</t>
@@ -1785,8 +1686,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2360,144 +2262,144 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
+        <v>59</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -2506,18 +2408,18 @@
         <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -2526,18 +2428,18 @@
         <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -2546,18 +2448,18 @@
         <v>33</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -2566,754 +2468,754 @@
         <v>33</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
+        <v>71</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
         <v>36</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>88</v>
+        <v>74</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>92</v>
+        <v>77</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
+        <v>83</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
+        <v>86</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
+        <v>89</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H26" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
+        <v>92</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H27" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" t="s">
-        <v>116</v>
+        <v>95</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" t="s">
-        <v>120</v>
+        <v>98</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="H29" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
+        <v>101</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
+        <v>104</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H31" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32" t="s">
-        <v>120</v>
+        <v>107</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" t="s">
-        <v>133</v>
+        <v>110</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
+        <v>113</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H34" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
-      </c>
-      <c r="C35" t="s">
-        <v>140</v>
+        <v>116</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H35" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
-      </c>
-      <c r="C36" t="s">
-        <v>140</v>
+        <v>119</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H36" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" t="s">
-        <v>147</v>
+        <v>122</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H37" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" t="s">
-        <v>147</v>
+        <v>125</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" t="s">
-        <v>154</v>
+        <v>128</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="B40" t="s">
-        <v>157</v>
-      </c>
-      <c r="C40" t="s">
-        <v>154</v>
+        <v>131</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>160</v>
-      </c>
-      <c r="C41" t="s">
-        <v>154</v>
+        <v>134</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
-        <v>163</v>
-      </c>
-      <c r="C42" t="s">
-        <v>164</v>
+        <v>137</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H42" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" t="s">
-        <v>164</v>
+        <v>140</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H43" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
-      </c>
-      <c r="C44" t="s">
-        <v>171</v>
+        <v>143</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>174</v>
-      </c>
-      <c r="C45" t="s">
-        <v>171</v>
+        <v>146</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
-      </c>
-      <c r="C46" t="s">
-        <v>171</v>
+        <v>149</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s">
-        <v>180</v>
-      </c>
-      <c r="C47" t="s">
-        <v>181</v>
+        <v>152</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="B48" t="s">
-        <v>184</v>
-      </c>
-      <c r="C48" t="s">
-        <v>181</v>
+        <v>155</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="B49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C49" t="s">
-        <v>188</v>
+        <v>158</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B50" t="s">
-        <v>191</v>
-      </c>
-      <c r="C50" t="s">
-        <v>188</v>
+        <v>161</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
-      </c>
-      <c r="C51" t="s">
-        <v>194</v>
+        <v>163</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
-      </c>
-      <c r="C52" t="s">
-        <v>194</v>
+        <v>166</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
-      </c>
-      <c r="C53" t="s">
-        <v>201</v>
+        <v>169</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
-      </c>
-      <c r="C54" t="s">
-        <v>201</v>
+        <v>172</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B55" t="s">
-        <v>207</v>
-      </c>
-      <c r="C55" t="s">
-        <v>208</v>
+        <v>175</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
-      </c>
-      <c r="C56" t="s">
-        <v>208</v>
+        <v>178</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 D2:D3 G2:H3 A13:D56 D7:D12 A2:A12 G13:H56 H4:H12" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 D2:D3 G2:H3 A13:B13 A14:B56 D7:D8 A2:A12 G13:H56 H4:H12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3333,142 +3235,142 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="B1" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="C1" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="D1" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="E1" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="F1" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D6" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="F6" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="E7" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3476,19 +3378,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3496,379 +3398,379 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D12" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D13" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="F13" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="B14" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="F15" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B18" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="E18" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="F18" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="E19" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="F19" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="F20" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" t="s">
         <v>228</v>
-      </c>
-      <c r="D21" t="s">
-        <v>261</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D22" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C24" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="E24" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="F24" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C25" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D25" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="E25" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="F25" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D26" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C27" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D27" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E27" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F27" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3876,19 +3778,19 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D28" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3896,179 +3798,179 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D29" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C30" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D30" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="E30" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="F30" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C31" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="F31" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D32" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="E32" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F32" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D33" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D34" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C36" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D36" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="E36" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="F36" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B37" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="E37" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="F37" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4076,19 +3978,19 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D38" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="E38" t="s">
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4096,219 +3998,219 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D39" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="E39" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="E40" t="s">
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C41" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D41" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="E41" t="s">
         <v>12</v>
       </c>
       <c r="F41" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C42" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D42" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="E42" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="F42" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D43" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="E43" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="F43" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C44" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D44" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="E44" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="F44" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C45" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D45" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="E45" t="s">
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C46" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D46" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="E46" t="s">
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D47" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C48" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D48" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="E48" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="F48" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="E49" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="F49" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4316,19 +4218,19 @@
         <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C50" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D50" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="E50" t="s">
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4336,19 +4238,19 @@
         <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="E51" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F51" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4356,19 +4258,19 @@
         <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C52" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="E52" t="s">
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4376,899 +4278,899 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="E53" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D54" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="E54" t="s">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="F54" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C55" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="E55" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="F55" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D56" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="E56" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="F56" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D57" t="s">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="E57" t="s">
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B58" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D58" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="E58" t="s">
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D59" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="E59" t="s">
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C60" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="E60" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="F60" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C61" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D61" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="E61" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="F61" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C63" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="E63" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="F63" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B64" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D64" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="E64" t="s">
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C65" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D65" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="E65" t="s">
         <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C66" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="E66" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="F66" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C67" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D67" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="E67" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="F67" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C68" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="E68" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="F68" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="B69" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D69" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="E69" t="s">
         <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B70" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C70" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="E70" t="s">
         <v>12</v>
       </c>
       <c r="F70" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="E71" t="s">
         <v>12</v>
       </c>
       <c r="F71" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="B72" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C72" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="E72" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="F72" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="B73" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C73" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="E73" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="F73" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C74" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D74" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="E74" t="s">
         <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C75" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D75" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="E75" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="F75" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E76" t="s">
         <v>12</v>
       </c>
       <c r="F76" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C77" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="E77" t="s">
         <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C78" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="E78" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="F78" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C79" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="E79" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="F79" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C80" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="E80" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="F80" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D81" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="E81" t="s">
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="B82" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="E82" t="s">
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="B83" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C83" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="E83" t="s">
         <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="E84" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="F84" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B85" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C85" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="E85" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="F85" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C86" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="E86" t="s">
         <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C87" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="E87" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="F87" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B88" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="E88" t="s">
         <v>12</v>
       </c>
       <c r="F88" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B89" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C89" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B90" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C90" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="E90" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="F90" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B91" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="E91" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="F91" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="E92" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="F92" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B93" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C93" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D93" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="E93" t="s">
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B94" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C94" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="E94" t="s">
         <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="E95" t="s">
         <v>12</v>
       </c>
       <c r="F95" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="B96" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="E96" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="F96" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
+        <v>168</v>
+      </c>
+      <c r="B97" t="s">
         <v>199</v>
       </c>
-      <c r="B97" t="s">
-        <v>232</v>
-      </c>
       <c r="C97" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D97" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="E97" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="F97" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -5276,19 +5178,19 @@
         <v>30</v>
       </c>
       <c r="B98" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C98" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D98" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="E98" t="s">
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -5296,59 +5198,59 @@
         <v>30</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C99" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D99" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="E99" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="F99" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D100" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="E100" t="s">
         <v>12</v>
       </c>
       <c r="F100" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B101" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C101" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D101" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="E101" t="s">
         <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5356,19 +5258,19 @@
         <v>23</v>
       </c>
       <c r="B102" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C102" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="E102" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -5376,139 +5278,139 @@
         <v>23</v>
       </c>
       <c r="B103" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C103" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="D103" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="E103" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B104" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C104" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D104" t="s">
-        <v>370</v>
+        <v>337</v>
       </c>
       <c r="E104" t="s">
-        <v>371</v>
+        <v>338</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B105" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C105" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="E105" t="s">
         <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="C106" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="E106" t="s">
         <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="E107" t="s">
         <v>12</v>
       </c>
       <c r="F107" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C108" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="E108" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B109" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="C109" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="E109" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="F109" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/data/sample-data-55emp-6proj.xlsx
+++ b/src/assets/data/sample-data-55emp-6proj.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="208">
   <si>
     <t>ID</t>
   </si>
@@ -144,22 +144,25 @@
     <t>Bùi Phan Viết Cường</t>
   </si>
   <si>
+    <t>Tech Lead</t>
+  </si>
+  <si>
+    <t>CUONGBPV@fpt.com</t>
+  </si>
+  <si>
+    <t>NV008</t>
+  </si>
+  <si>
+    <t>Vương Trọng Khang</t>
+  </si>
+  <si>
+    <t>KHANGVT5@fpt.com</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Thắng</t>
+  </si>
+  <si>
     <t>Dev Lead</t>
-  </si>
-  <si>
-    <t>CUONGBPV@fpt.com</t>
-  </si>
-  <si>
-    <t>NV008</t>
-  </si>
-  <si>
-    <t>Vương Trọng Khang</t>
-  </si>
-  <si>
-    <t>KHANGVT5@fpt.com</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồng Thắng</t>
   </si>
   <si>
     <t>THANGNH29@fpt.com</t>
@@ -1864,13 +1867,13 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -1878,19 +1881,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
@@ -1898,10 +1901,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -1910,7 +1913,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -1918,10 +1921,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -1930,18 +1933,18 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1950,7 +1953,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
         <v>35</v>
@@ -1958,10 +1961,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -1970,7 +1973,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -1978,19 +1981,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
@@ -1998,19 +2001,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
@@ -2018,19 +2021,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
@@ -2038,19 +2041,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
@@ -2058,19 +2061,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
@@ -2078,39 +2081,39 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
         <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s">
         <v>18</v>
@@ -2118,19 +2121,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
         <v>35</v>
@@ -2138,19 +2141,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
         <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s">
         <v>35</v>
@@ -2158,19 +2161,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s">
         <v>35</v>
@@ -2178,19 +2181,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
         <v>18</v>
@@ -2198,10 +2201,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -2210,7 +2213,7 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
@@ -2218,19 +2221,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
@@ -2238,10 +2241,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
@@ -2250,58 +2253,58 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
         <v>28</v>
@@ -2310,18 +2313,18 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -2330,158 +2333,158 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
         <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
         <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
         <v>28</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -2490,7 +2493,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -2498,10 +2501,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
         <v>33</v>
@@ -2510,18 +2513,18 @@
         <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -2530,7 +2533,7 @@
         <v>11</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G43" t="s">
         <v>14</v>
@@ -2538,19 +2541,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
@@ -2558,210 +2561,210 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G49" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G51" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s">
         <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G52" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C53" t="s">
         <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G53" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C54" t="s">
         <v>28</v>
       </c>
       <c r="D54" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -2770,7 +2773,7 @@
         <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G55" t="s">
         <v>35</v>
@@ -2778,70 +2781,70 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G56" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
         <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G57" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C59" t="s">
         <v>33</v>
@@ -2850,7 +2853,7 @@
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G59" t="s">
         <v>14</v>
@@ -2863,7 +2866,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="G2:G3 F1:H1 A1:D1 A2" numberStoredAsText="1"/>
+    <ignoredError sqref="A2 A1:D1 F1:H1 G2:G3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2882,22 +2885,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2905,14 +2908,14 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C2" t="str">
         <f>+VLOOKUP(A2,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2920,14 +2923,14 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3" t="str">
         <f>+VLOOKUP(A3,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2935,14 +2938,14 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C4" t="str">
         <f>+VLOOKUP(A4,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2950,14 +2953,14 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C5" t="str">
         <f>+VLOOKUP(A5,'Nhân sự'!$A:$C,3,0)</f>
         <v>QC Lead</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2965,14 +2968,14 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C6" t="str">
         <f>+VLOOKUP(A6,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2980,14 +2983,14 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C7" t="str">
         <f>+VLOOKUP(A7,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2995,14 +2998,14 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C8" t="str">
         <f>+VLOOKUP(A8,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev Lead</v>
+        <v>Tech Lead</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3010,14 +3013,14 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C9" t="str">
         <f>+VLOOKUP(A9,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3025,719 +3028,719 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C10" t="str">
         <f>+VLOOKUP(A10,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C11" t="str">
         <f>+VLOOKUP(A11,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C12" t="str">
         <f>+VLOOKUP(A12,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C13" t="str">
         <f>+VLOOKUP(A13,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" t="str">
         <f>+VLOOKUP(A14,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C15" t="str">
         <f>+VLOOKUP(A15,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" t="str">
         <f>+VLOOKUP(A16,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" t="str">
         <f>+VLOOKUP(A17,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" t="str">
         <f>+VLOOKUP(A18,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA Lead</v>
       </c>
       <c r="F18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" t="str">
         <f>+VLOOKUP(A19,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" t="str">
         <f>+VLOOKUP(A20,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" t="str">
         <f>+VLOOKUP(A21,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C22" t="str">
         <f>+VLOOKUP(A22,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C23" t="str">
         <f>+VLOOKUP(A23,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C24" t="str">
         <f>+VLOOKUP(A24,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C25" t="str">
         <f>+VLOOKUP(A25,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" t="str">
         <f>+VLOOKUP(A26,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C27" t="str">
         <f>+VLOOKUP(A27,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C28" t="str">
         <f>+VLOOKUP(A28,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" t="str">
         <f>+VLOOKUP(A29,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C30" t="str">
         <f>+VLOOKUP(A30,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C31" t="str">
         <f>+VLOOKUP(A31,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C32" t="str">
         <f>+VLOOKUP(A32,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C33" t="str">
         <f>+VLOOKUP(A33,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F33" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C34" t="str">
         <f>+VLOOKUP(A34,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" t="str">
         <f>+VLOOKUP(A35,'Nhân sự'!$A:$C,3,0)</f>
         <v>QC Lead</v>
       </c>
       <c r="F35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C36" t="str">
         <f>+VLOOKUP(A36,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C37" t="str">
         <f>+VLOOKUP(A37,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F37" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C38" t="str">
         <f>+VLOOKUP(A38,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F38" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C39" t="str">
         <f>+VLOOKUP(A39,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" t="str">
         <f>+VLOOKUP(A40,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C41" t="str">
         <f>+VLOOKUP(A41,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" t="str">
         <f>+VLOOKUP(A42,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C43" t="str">
         <f>+VLOOKUP(A43,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F43" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C44" t="str">
         <f>+VLOOKUP(A44,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F44" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C45" t="str">
         <f>+VLOOKUP(A45,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F45" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C46" t="str">
         <f>+VLOOKUP(A46,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F46" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C47" t="str">
         <f>+VLOOKUP(A47,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F47" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C48" t="str">
         <f>+VLOOKUP(A48,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F48" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C49" t="str">
         <f>+VLOOKUP(A49,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C50" t="str">
         <f>+VLOOKUP(A50,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C51" t="str">
         <f>+VLOOKUP(A51,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C52" t="str">
         <f>+VLOOKUP(A52,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C53" t="str">
         <f>+VLOOKUP(A53,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C54" t="str">
         <f>+VLOOKUP(A54,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C55" t="str">
         <f>+VLOOKUP(A55,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C56" t="str">
         <f>+VLOOKUP(A56,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C57" t="str">
         <f>+VLOOKUP(A57,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3745,29 +3748,29 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C58" t="str">
         <f>+VLOOKUP(A58,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" t="str">
         <f>+VLOOKUP(A59,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:6">
@@ -3775,21 +3778,21 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C60" t="str">
         <f>+VLOOKUP(A60,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="F2 A1:F1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 F2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/data/sample-data-55emp-6proj.xlsx
+++ b/src/assets/data/sample-data-55emp-6proj.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="215">
   <si>
     <t>ID</t>
   </si>
@@ -616,6 +616,27 @@
   </si>
   <si>
     <t>PHUONGNT204@fpt.com</t>
+  </si>
+  <si>
+    <t>NV059</t>
+  </si>
+  <si>
+    <t>Trần Thụy Thủy Tiên</t>
+  </si>
+  <si>
+    <t>PMO</t>
+  </si>
+  <si>
+    <t>TienTTT14@fpt.com</t>
+  </si>
+  <si>
+    <t>NV060</t>
+  </si>
+  <si>
+    <t>Hà Thúy Ngọc</t>
+  </si>
+  <si>
+    <t>NgocHT30@fpt.com</t>
   </si>
   <si>
     <t>ID nhân viên</t>
@@ -676,18 +697,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1130,28 +1151,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1275,8 +1296,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1661,7 +1683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.8" customWidth="1"/>
@@ -1712,7 +1734,7 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
@@ -1732,7 +1754,7 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
@@ -1752,7 +1774,7 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G4" t="s">
@@ -1772,7 +1794,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G5" t="s">
@@ -1792,7 +1814,7 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G6" t="s">
@@ -1812,7 +1834,7 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G7" t="s">
@@ -1832,7 +1854,7 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
@@ -1852,7 +1874,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G9" t="s">
@@ -1872,7 +1894,7 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G10" t="s">
@@ -1892,7 +1914,7 @@
       <c r="D11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G11" t="s">
@@ -1912,7 +1934,7 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G12" t="s">
@@ -1932,7 +1954,7 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G13" t="s">
@@ -1952,7 +1974,7 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G14" t="s">
@@ -1972,7 +1994,7 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>59</v>
       </c>
       <c r="G15" t="s">
@@ -1992,7 +2014,7 @@
       <c r="D16" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G16" t="s">
@@ -2012,7 +2034,7 @@
       <c r="D17" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G17" t="s">
@@ -2032,7 +2054,7 @@
       <c r="D18" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" t="s">
@@ -2052,7 +2074,7 @@
       <c r="D19" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G19" t="s">
@@ -2072,7 +2094,7 @@
       <c r="D20" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G20" t="s">
@@ -2092,7 +2114,7 @@
       <c r="D21" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>80</v>
       </c>
       <c r="G21" t="s">
@@ -2112,7 +2134,7 @@
       <c r="D22" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G22" t="s">
@@ -2132,7 +2154,7 @@
       <c r="D23" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G23" t="s">
@@ -2152,7 +2174,7 @@
       <c r="D24" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" t="s">
@@ -2172,7 +2194,7 @@
       <c r="D25" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G25" t="s">
@@ -2192,7 +2214,7 @@
       <c r="D26" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>95</v>
       </c>
       <c r="G26" t="s">
@@ -2212,7 +2234,7 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>98</v>
       </c>
       <c r="G27" t="s">
@@ -2232,7 +2254,7 @@
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>101</v>
       </c>
       <c r="G28" t="s">
@@ -2252,7 +2274,7 @@
       <c r="D29" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>104</v>
       </c>
       <c r="G29" t="s">
@@ -2272,7 +2294,7 @@
       <c r="D30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G30" t="s">
@@ -2292,7 +2314,7 @@
       <c r="D31" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>110</v>
       </c>
       <c r="G31" t="s">
@@ -2312,7 +2334,7 @@
       <c r="D32" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>113</v>
       </c>
       <c r="G32" t="s">
@@ -2332,7 +2354,7 @@
       <c r="D33" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>116</v>
       </c>
       <c r="G33" t="s">
@@ -2352,7 +2374,7 @@
       <c r="D34" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>119</v>
       </c>
       <c r="G34" t="s">
@@ -2372,7 +2394,7 @@
       <c r="D35" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>122</v>
       </c>
       <c r="G35" t="s">
@@ -2392,7 +2414,7 @@
       <c r="D36" t="s">
         <v>63</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>125</v>
       </c>
       <c r="G36" t="s">
@@ -2412,7 +2434,7 @@
       <c r="D37" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>128</v>
       </c>
       <c r="G37" t="s">
@@ -2432,7 +2454,7 @@
       <c r="D38" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>131</v>
       </c>
       <c r="G38" t="s">
@@ -2452,7 +2474,7 @@
       <c r="D39" t="s">
         <v>63</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>134</v>
       </c>
       <c r="G39" t="s">
@@ -2472,7 +2494,7 @@
       <c r="D40" t="s">
         <v>63</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>137</v>
       </c>
       <c r="G40" t="s">
@@ -2492,7 +2514,7 @@
       <c r="D41" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>140</v>
       </c>
       <c r="G41" t="s">
@@ -2512,7 +2534,7 @@
       <c r="D42" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>143</v>
       </c>
       <c r="G42" t="s">
@@ -2532,7 +2554,7 @@
       <c r="D43" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>146</v>
       </c>
       <c r="G43" t="s">
@@ -2552,7 +2574,7 @@
       <c r="D44" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G44" t="s">
@@ -2572,7 +2594,7 @@
       <c r="D45" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>152</v>
       </c>
       <c r="G45" t="s">
@@ -2592,7 +2614,7 @@
       <c r="D46" t="s">
         <v>63</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>155</v>
       </c>
       <c r="G46" t="s">
@@ -2612,7 +2634,7 @@
       <c r="D47" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>158</v>
       </c>
       <c r="G47" t="s">
@@ -2632,7 +2654,7 @@
       <c r="D48" t="s">
         <v>63</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>161</v>
       </c>
       <c r="G48" t="s">
@@ -2652,7 +2674,7 @@
       <c r="D49" t="s">
         <v>63</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>164</v>
       </c>
       <c r="G49" t="s">
@@ -2672,7 +2694,7 @@
       <c r="D50" t="s">
         <v>63</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>167</v>
       </c>
       <c r="G50" t="s">
@@ -2692,7 +2714,7 @@
       <c r="D51" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>170</v>
       </c>
       <c r="G51" t="s">
@@ -2712,7 +2734,7 @@
       <c r="D52" t="s">
         <v>63</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="2" t="s">
         <v>173</v>
       </c>
       <c r="G52" t="s">
@@ -2732,7 +2754,7 @@
       <c r="D53" t="s">
         <v>63</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>176</v>
       </c>
       <c r="G53" t="s">
@@ -2752,7 +2774,7 @@
       <c r="D54" t="s">
         <v>63</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>179</v>
       </c>
       <c r="G54" t="s">
@@ -2772,7 +2794,7 @@
       <c r="D55" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="2" t="s">
         <v>182</v>
       </c>
       <c r="G55" t="s">
@@ -2792,7 +2814,7 @@
       <c r="D56" t="s">
         <v>63</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="2" t="s">
         <v>185</v>
       </c>
       <c r="G56" t="s">
@@ -2812,7 +2834,7 @@
       <c r="D57" t="s">
         <v>63</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="2" t="s">
         <v>188</v>
       </c>
       <c r="G57" t="s">
@@ -2832,7 +2854,7 @@
       <c r="D58" t="s">
         <v>11</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="2" t="s">
         <v>191</v>
       </c>
       <c r="G58" t="s">
@@ -2852,21 +2874,65 @@
       <c r="D59" t="s">
         <v>11</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="2" t="s">
         <v>194</v>
       </c>
       <c r="G59" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:7">
+      <c r="A60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C60" t="s">
+        <v>197</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:7">
+      <c r="A61" t="s">
+        <v>199</v>
+      </c>
+      <c r="B61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C61" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G61" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H59" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="E60" r:id="rId1" display="TienTTT14@fpt.com"/>
+    <hyperlink ref="E61" r:id="rId2" display="NgocHT30@fpt.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A2 A1:D1 F1:H1 G2:G3" numberStoredAsText="1"/>
+    <ignoredError sqref="G2:G3 F1:H1 A1:D1 A2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2885,22 +2951,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2908,14 +2974,14 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C2" t="str">
         <f>+VLOOKUP(A2,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2923,14 +2989,14 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C3" t="str">
         <f>+VLOOKUP(A3,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2938,14 +3004,14 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C4" t="str">
         <f>+VLOOKUP(A4,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2953,14 +3019,14 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C5" t="str">
         <f>+VLOOKUP(A5,'Nhân sự'!$A:$C,3,0)</f>
         <v>QC Lead</v>
       </c>
       <c r="F5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2968,14 +3034,14 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C6" t="str">
         <f>+VLOOKUP(A6,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2983,14 +3049,14 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C7" t="str">
         <f>+VLOOKUP(A7,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2998,14 +3064,14 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C8" t="str">
         <f>+VLOOKUP(A8,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tech Lead</v>
       </c>
       <c r="F8" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3013,14 +3079,14 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C9" t="str">
         <f>+VLOOKUP(A9,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3028,14 +3094,14 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C10" t="str">
         <f>+VLOOKUP(A10,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F10" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3043,14 +3109,14 @@
         <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C11" t="str">
         <f>+VLOOKUP(A11,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F11" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3058,14 +3124,14 @@
         <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C12" t="str">
         <f>+VLOOKUP(A12,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F12" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3073,14 +3139,14 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C13" t="str">
         <f>+VLOOKUP(A13,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F13" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3088,14 +3154,14 @@
         <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C14" t="str">
         <f>+VLOOKUP(A14,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F14" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3103,14 +3169,14 @@
         <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C15" t="str">
         <f>+VLOOKUP(A15,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F15" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3118,14 +3184,14 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C16" t="str">
         <f>+VLOOKUP(A16,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3133,14 +3199,14 @@
         <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C17" t="str">
         <f>+VLOOKUP(A17,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F17" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3148,14 +3214,14 @@
         <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C18" t="str">
         <f>+VLOOKUP(A18,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA Lead</v>
       </c>
       <c r="F18" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3163,14 +3229,14 @@
         <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C19" t="str">
         <f>+VLOOKUP(A19,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3178,14 +3244,14 @@
         <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C20" t="str">
         <f>+VLOOKUP(A20,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F20" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3193,14 +3259,14 @@
         <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C21" t="str">
         <f>+VLOOKUP(A21,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F21" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3208,14 +3274,14 @@
         <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C22" t="str">
         <f>+VLOOKUP(A22,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F22" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3223,14 +3289,14 @@
         <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C23" t="str">
         <f>+VLOOKUP(A23,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F23" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3238,14 +3304,14 @@
         <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C24" t="str">
         <f>+VLOOKUP(A24,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F24" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3253,14 +3319,14 @@
         <v>90</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C25" t="str">
         <f>+VLOOKUP(A25,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F25" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3268,14 +3334,14 @@
         <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C26" t="str">
         <f>+VLOOKUP(A26,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F26" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3283,14 +3349,14 @@
         <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C27" t="str">
         <f>+VLOOKUP(A27,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F27" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3298,14 +3364,14 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C28" t="str">
         <f>+VLOOKUP(A28,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F28" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3313,14 +3379,14 @@
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C29" t="str">
         <f>+VLOOKUP(A29,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F29" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3328,14 +3394,14 @@
         <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C30" t="str">
         <f>+VLOOKUP(A30,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F30" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -3343,14 +3409,14 @@
         <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C31" t="str">
         <f>+VLOOKUP(A31,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F31" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3358,14 +3424,14 @@
         <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C32" t="str">
         <f>+VLOOKUP(A32,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F32" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3373,14 +3439,14 @@
         <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C33" t="str">
         <f>+VLOOKUP(A33,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3388,14 +3454,14 @@
         <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C34" t="str">
         <f>+VLOOKUP(A34,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3403,14 +3469,14 @@
         <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C35" t="str">
         <f>+VLOOKUP(A35,'Nhân sự'!$A:$C,3,0)</f>
         <v>QC Lead</v>
       </c>
       <c r="F35" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3418,14 +3484,14 @@
         <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C36" t="str">
         <f>+VLOOKUP(A36,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F36" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3433,14 +3499,14 @@
         <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C37" t="str">
         <f>+VLOOKUP(A37,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F37" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3448,14 +3514,14 @@
         <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C38" t="str">
         <f>+VLOOKUP(A38,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F38" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -3463,14 +3529,14 @@
         <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C39" t="str">
         <f>+VLOOKUP(A39,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F39" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3478,14 +3544,14 @@
         <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C40" t="str">
         <f>+VLOOKUP(A40,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F40" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -3493,14 +3559,14 @@
         <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C41" t="str">
         <f>+VLOOKUP(A41,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F41" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3508,14 +3574,14 @@
         <v>141</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C42" t="str">
         <f>+VLOOKUP(A42,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F42" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -3523,14 +3589,14 @@
         <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C43" t="str">
         <f>+VLOOKUP(A43,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F43" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3538,14 +3604,14 @@
         <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C44" t="str">
         <f>+VLOOKUP(A44,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F44" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3553,14 +3619,14 @@
         <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C45" t="str">
         <f>+VLOOKUP(A45,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F45" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3568,14 +3634,14 @@
         <v>153</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C46" t="str">
         <f>+VLOOKUP(A46,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F46" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3583,14 +3649,14 @@
         <v>156</v>
       </c>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C47" t="str">
         <f>+VLOOKUP(A47,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F47" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3598,14 +3664,14 @@
         <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C48" t="str">
         <f>+VLOOKUP(A48,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F48" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3613,14 +3679,14 @@
         <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C49" t="str">
         <f>+VLOOKUP(A49,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F49" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3628,14 +3694,14 @@
         <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C50" t="str">
         <f>+VLOOKUP(A50,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F50" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3643,14 +3709,14 @@
         <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C51" t="str">
         <f>+VLOOKUP(A51,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F51" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3658,14 +3724,14 @@
         <v>171</v>
       </c>
       <c r="B52" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C52" t="str">
         <f>+VLOOKUP(A52,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F52" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3673,14 +3739,14 @@
         <v>174</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C53" t="str">
         <f>+VLOOKUP(A53,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F53" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3688,14 +3754,14 @@
         <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C54" t="str">
         <f>+VLOOKUP(A54,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F54" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3703,14 +3769,14 @@
         <v>180</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C55" t="str">
         <f>+VLOOKUP(A55,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F55" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3718,14 +3784,14 @@
         <v>183</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C56" t="str">
         <f>+VLOOKUP(A56,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F56" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3733,14 +3799,14 @@
         <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C57" t="str">
         <f>+VLOOKUP(A57,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F57" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3748,14 +3814,14 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C58" t="str">
         <f>+VLOOKUP(A58,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F58" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3763,14 +3829,14 @@
         <v>192</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C59" t="str">
         <f>+VLOOKUP(A59,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F59" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:6">
@@ -3778,21 +3844,21 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C60" t="str">
         <f>+VLOOKUP(A60,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F60" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 F2" numberStoredAsText="1"/>
+    <ignoredError sqref="F2 A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/data/sample-data-55emp-6proj.xlsx
+++ b/src/assets/data/sample-data-55emp-6proj.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12285"/>
+    <workbookView windowWidth="28800" windowHeight="10860" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Nhân sự" sheetId="1" r:id="rId1"/>
     <sheet name="Dự án" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nhân sự'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nhân sự'!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="334">
   <si>
     <t>ID</t>
   </si>
@@ -144,7 +144,7 @@
     <t>Bùi Phan Viết Cường</t>
   </si>
   <si>
-    <t>Tech Lead</t>
+    <t>Dev Lead</t>
   </si>
   <si>
     <t>CUONGBPV@fpt.com</t>
@@ -162,9 +162,6 @@
     <t>Nguyễn Hồng Thắng</t>
   </si>
   <si>
-    <t>Dev Lead</t>
-  </si>
-  <si>
     <t>THANGNH29@fpt.com</t>
   </si>
   <si>
@@ -621,22 +618,364 @@
     <t>NV059</t>
   </si>
   <si>
-    <t>Trần Thụy Thủy Tiên</t>
-  </si>
-  <si>
-    <t>PMO</t>
-  </si>
-  <si>
-    <t>TienTTT14@fpt.com</t>
+    <t>Huỳnh Thiện Nhân</t>
+  </si>
+  <si>
+    <t>Intern</t>
+  </si>
+  <si>
+    <t>NHANHT@fpt.com</t>
   </si>
   <si>
     <t>NV060</t>
   </si>
   <si>
-    <t>Hà Thúy Ngọc</t>
-  </si>
-  <si>
-    <t>NgocHT30@fpt.com</t>
+    <t>Mai Văn Vũ</t>
+  </si>
+  <si>
+    <t>VUMV2@fpt.com</t>
+  </si>
+  <si>
+    <t>NV061</t>
+  </si>
+  <si>
+    <t>Huỳnh Đức Phú</t>
+  </si>
+  <si>
+    <t>PHUHD5@fpt.com</t>
+  </si>
+  <si>
+    <t>NV062</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Nhân</t>
+  </si>
+  <si>
+    <t>NHANNT194@fpt.com</t>
+  </si>
+  <si>
+    <t>NV063</t>
+  </si>
+  <si>
+    <t>Bùi Gia Huy</t>
+  </si>
+  <si>
+    <t>HUYBG@fpt.com</t>
+  </si>
+  <si>
+    <t>NV064</t>
+  </si>
+  <si>
+    <t>Trà Nhật Đông</t>
+  </si>
+  <si>
+    <t>DONGTN2@fpt.com</t>
+  </si>
+  <si>
+    <t>NV065</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hồng Yến</t>
+  </si>
+  <si>
+    <t>YENNTH109@fpt.com</t>
+  </si>
+  <si>
+    <t>NV066</t>
+  </si>
+  <si>
+    <t>Trương Ngọc Thảo</t>
+  </si>
+  <si>
+    <t>QC/QA</t>
+  </si>
+  <si>
+    <t>THAOTN8@fpt.com</t>
+  </si>
+  <si>
+    <t>NV067</t>
+  </si>
+  <si>
+    <t>Lê Duy Hoàng Linh</t>
+  </si>
+  <si>
+    <t>LINHLDH@fpt.com</t>
+  </si>
+  <si>
+    <t>NV068</t>
+  </si>
+  <si>
+    <t>Trần Hoàng Phương</t>
+  </si>
+  <si>
+    <t>PHUONGTH24@fpt.com</t>
+  </si>
+  <si>
+    <t>NV069</t>
+  </si>
+  <si>
+    <t>Võ Minh Đạt</t>
+  </si>
+  <si>
+    <t>DATVM12@fpt.com</t>
+  </si>
+  <si>
+    <t>NV070</t>
+  </si>
+  <si>
+    <t>Hoàng Phi Hùng</t>
+  </si>
+  <si>
+    <t>HUNGHP5@fpt.com</t>
+  </si>
+  <si>
+    <t>NV071</t>
+  </si>
+  <si>
+    <t>Bùi Khánh Đang</t>
+  </si>
+  <si>
+    <t>DANGBK@fpt.com</t>
+  </si>
+  <si>
+    <t>NV072</t>
+  </si>
+  <si>
+    <t>Vũ Ngọc Thuỳ Anh</t>
+  </si>
+  <si>
+    <t>Designer</t>
+  </si>
+  <si>
+    <t>ANHVNT3@fpt.com</t>
+  </si>
+  <si>
+    <t>NV073</t>
+  </si>
+  <si>
+    <t>Kiều Thành Phát</t>
+  </si>
+  <si>
+    <t>PHATKT2@fpt.com</t>
+  </si>
+  <si>
+    <t>NV074</t>
+  </si>
+  <si>
+    <t>Nguyễn Phùng Tài</t>
+  </si>
+  <si>
+    <t>TAINP17@fpt.com</t>
+  </si>
+  <si>
+    <t>NV075</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Anh</t>
+  </si>
+  <si>
+    <t>Tester cho HDBank, BA cho dự án blockchain</t>
+  </si>
+  <si>
+    <t>ANHND194@fpt.com</t>
+  </si>
+  <si>
+    <t>NV076</t>
+  </si>
+  <si>
+    <t>Phạm Hiếu Nghĩa</t>
+  </si>
+  <si>
+    <t>NGHIAPH12@fpt.com</t>
+  </si>
+  <si>
+    <t>NV077</t>
+  </si>
+  <si>
+    <t>Phạm Thị Diệu Linh</t>
+  </si>
+  <si>
+    <t>LINHPTD9@fpt.com</t>
+  </si>
+  <si>
+    <t>NV078</t>
+  </si>
+  <si>
+    <t>Phan Thị Kim Truyền</t>
+  </si>
+  <si>
+    <t>TRUYENPTK@fpt.com</t>
+  </si>
+  <si>
+    <t>NV079</t>
+  </si>
+  <si>
+    <t>Bùi Thị Thanh Ngân</t>
+  </si>
+  <si>
+    <t>NGANBTT9@fpt.com</t>
+  </si>
+  <si>
+    <t>NV080</t>
+  </si>
+  <si>
+    <t>Lục Chấn Toàn</t>
+  </si>
+  <si>
+    <t>TOANLC7@fpt.com</t>
+  </si>
+  <si>
+    <t>NV081</t>
+  </si>
+  <si>
+    <t>Trần Việt Quang</t>
+  </si>
+  <si>
+    <t>QuangTV33@fpt.com</t>
+  </si>
+  <si>
+    <t>NV082</t>
+  </si>
+  <si>
+    <t>Nguyễn Châu Phi</t>
+  </si>
+  <si>
+    <t>PHINC3@fpt.com</t>
+  </si>
+  <si>
+    <t>NV083</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Mỹ Anh</t>
+  </si>
+  <si>
+    <t>ANHLHM4@fpt.com</t>
+  </si>
+  <si>
+    <t>NV084</t>
+  </si>
+  <si>
+    <t>Ngô Nguyễn Cẩm Vi</t>
+  </si>
+  <si>
+    <t>VINNC@fpt.com</t>
+  </si>
+  <si>
+    <t>NV085</t>
+  </si>
+  <si>
+    <t>Phan Ngọc Tuấn Vinh</t>
+  </si>
+  <si>
+    <t>VINHPNT@FPT.COM@fpt.com</t>
+  </si>
+  <si>
+    <t>NV086</t>
+  </si>
+  <si>
+    <t>Đoàn Việt Hoàng</t>
+  </si>
+  <si>
+    <t>HOANGDV40@fpt.com</t>
+  </si>
+  <si>
+    <t>NV087</t>
+  </si>
+  <si>
+    <t>Nghê Tài Phát</t>
+  </si>
+  <si>
+    <t>PHATNT48@fpt.com</t>
+  </si>
+  <si>
+    <t>NV088</t>
+  </si>
+  <si>
+    <t>Đinh Thế Quyền</t>
+  </si>
+  <si>
+    <t>QUYENDT21@fpt.com</t>
+  </si>
+  <si>
+    <t>NV089</t>
+  </si>
+  <si>
+    <t>Nguyễn Đặng Ngọc Phong</t>
+  </si>
+  <si>
+    <t>PHONGNDN4@fpt.com</t>
+  </si>
+  <si>
+    <t>NV090</t>
+  </si>
+  <si>
+    <t>Lương Đức Duy</t>
+  </si>
+  <si>
+    <t>DUYLD19@fpt.com</t>
+  </si>
+  <si>
+    <t>NV091</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Dũng</t>
+  </si>
+  <si>
+    <t>DUNGNH45@fpt.com</t>
+  </si>
+  <si>
+    <t>NV092</t>
+  </si>
+  <si>
+    <t>Huỳnh Nguyễn Thái Đăng</t>
+  </si>
+  <si>
+    <t>DangHNT@fpt.com@fpt.com</t>
+  </si>
+  <si>
+    <t>NV093</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc Bảo</t>
+  </si>
+  <si>
+    <t>BAONQ54@fpt.com</t>
+  </si>
+  <si>
+    <t>NV094</t>
+  </si>
+  <si>
+    <t>Phan Tất Thành</t>
+  </si>
+  <si>
+    <t>THANHPT63@fpt.com</t>
+  </si>
+  <si>
+    <t>NV095</t>
+  </si>
+  <si>
+    <t>Ngô Sỹ Bảo Duy</t>
+  </si>
+  <si>
+    <t>DUYNSB@fpt.com</t>
+  </si>
+  <si>
+    <t>NV096</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiện Đoan</t>
+  </si>
+  <si>
+    <t>DOANNT22@fpt.com</t>
+  </si>
+  <si>
+    <t>NV097</t>
+  </si>
+  <si>
+    <t>Nguyễn Thể Phụng</t>
+  </si>
+  <si>
+    <t>PhungNT15@fpt.com</t>
   </si>
   <si>
     <t>ID nhân viên</t>
@@ -657,18 +996,18 @@
     <t>Trạng thái</t>
   </si>
   <si>
+    <t>ACB NWF</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Đi HD Biz</t>
+  </si>
+  <si>
     <t>Eximbank</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>ACB NWF</t>
-  </si>
-  <si>
-    <t>Đi HD Biz</t>
-  </si>
-  <si>
     <t>PRU</t>
   </si>
   <si>
@@ -676,6 +1015,24 @@
   </si>
   <si>
     <t>HN</t>
+  </si>
+  <si>
+    <t>Phát triển Intern Hub</t>
+  </si>
+  <si>
+    <t>HDB DN</t>
+  </si>
+  <si>
+    <t>EIB_SO24-B-227_Điều chỉnh màn hình nộp/rút trên Teller app</t>
+  </si>
+  <si>
+    <t>BVB_AgentApp, HDB_IBMB_2024_PM</t>
+  </si>
+  <si>
+    <t>Project liên quan Akabot</t>
+  </si>
+  <si>
+    <t>Chưa vào ạ</t>
   </si>
 </sst>
 </file>
@@ -697,18 +1054,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1151,28 +1508,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1296,9 +1653,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1683,7 +2039,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.8" customWidth="1"/>
@@ -1734,7 +2090,7 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
@@ -1754,7 +2110,7 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
@@ -1774,7 +2130,7 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G4" t="s">
@@ -1794,7 +2150,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G5" t="s">
@@ -1814,7 +2170,7 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G6" t="s">
@@ -1834,7 +2190,7 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G7" t="s">
@@ -1854,7 +2210,7 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
@@ -1874,7 +2230,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>41</v>
       </c>
       <c r="G9" t="s">
@@ -1889,13 +2245,13 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>44</v>
+      <c r="E10" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -1903,19 +2259,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
+      <c r="E11" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
@@ -1923,10 +2279,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -1934,8 +2290,8 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>50</v>
+      <c r="E12" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -1943,10 +2299,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
         <v>51</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -1954,19 +2310,19 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
+      <c r="E13" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
         <v>54</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -1974,8 +2330,8 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>56</v>
+      <c r="E14" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="G14" t="s">
         <v>35</v>
@@ -1983,10 +2339,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
         <v>57</v>
-      </c>
-      <c r="B15" t="s">
-        <v>58</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -1994,8 +2350,8 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>59</v>
+      <c r="E15" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
@@ -2003,19 +2359,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
         <v>60</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>61</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>62</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
@@ -2023,19 +2379,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
         <v>65</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
@@ -2043,19 +2399,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
         <v>68</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>69</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
@@ -2063,19 +2419,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
         <v>72</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
@@ -2083,19 +2439,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
         <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
@@ -2103,39 +2459,39 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
         <v>78</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
         <v>81</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="G22" t="s">
         <v>18</v>
@@ -2143,19 +2499,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
         <v>84</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="G23" t="s">
         <v>35</v>
@@ -2163,19 +2519,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
         <v>87</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G24" t="s">
         <v>35</v>
@@ -2183,19 +2539,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
         <v>90</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G25" t="s">
         <v>35</v>
@@ -2203,19 +2559,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s">
         <v>93</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="G26" t="s">
         <v>18</v>
@@ -2223,10 +2579,10 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
         <v>96</v>
-      </c>
-      <c r="B27" t="s">
-        <v>97</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
@@ -2234,8 +2590,8 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>98</v>
+      <c r="E27" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
@@ -2243,19 +2599,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="B28" t="s">
-        <v>100</v>
-      </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>101</v>
+      <c r="E28" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
@@ -2263,10 +2619,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s">
         <v>102</v>
-      </c>
-      <c r="B29" t="s">
-        <v>103</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
@@ -2274,59 +2630,59 @@
       <c r="D29" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>104</v>
+      <c r="E29" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" t="s">
         <v>105</v>
       </c>
-      <c r="B30" t="s">
-        <v>106</v>
-      </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>107</v>
+      <c r="E30" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" t="s">
         <v>108</v>
       </c>
-      <c r="B31" t="s">
-        <v>109</v>
-      </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>110</v>
+      <c r="E31" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" t="s">
         <v>111</v>
-      </c>
-      <c r="B32" t="s">
-        <v>112</v>
       </c>
       <c r="C32" t="s">
         <v>28</v>
@@ -2334,19 +2690,19 @@
       <c r="D32" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>113</v>
+      <c r="E32" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
         <v>114</v>
-      </c>
-      <c r="B33" t="s">
-        <v>115</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -2354,159 +2710,159 @@
       <c r="D33" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>116</v>
+      <c r="E33" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="G33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" t="s">
         <v>117</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
         <v>120</v>
-      </c>
-      <c r="B35" t="s">
-        <v>121</v>
       </c>
       <c r="C35" t="s">
         <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>122</v>
+        <v>62</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="G35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
         <v>123</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="G36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" t="s">
         <v>126</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="G37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" t="s">
         <v>129</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="G38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" t="s">
         <v>132</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C39" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" t="s">
-        <v>63</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="G39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" t="s">
         <v>135</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" t="s">
-        <v>63</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
         <v>138</v>
-      </c>
-      <c r="B41" t="s">
-        <v>139</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -2514,8 +2870,8 @@
       <c r="D41" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>140</v>
+      <c r="E41" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -2523,10 +2879,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
+        <v>140</v>
+      </c>
+      <c r="B42" t="s">
         <v>141</v>
-      </c>
-      <c r="B42" t="s">
-        <v>142</v>
       </c>
       <c r="C42" t="s">
         <v>33</v>
@@ -2534,19 +2890,19 @@
       <c r="D42" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>143</v>
+      <c r="E42" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="G42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" t="s">
         <v>144</v>
-      </c>
-      <c r="B43" t="s">
-        <v>145</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -2554,8 +2910,8 @@
       <c r="D43" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>146</v>
+      <c r="E43" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="G43" t="s">
         <v>14</v>
@@ -2563,19 +2919,19 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" t="s">
         <v>147</v>
       </c>
-      <c r="B44" t="s">
-        <v>148</v>
-      </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>149</v>
+      <c r="E44" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="G44" t="s">
         <v>14</v>
@@ -2583,210 +2939,210 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" t="s">
         <v>150</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="G45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
         <v>153</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" t="s">
-        <v>63</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="G46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" t="s">
         <v>156</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C47" t="s">
-        <v>62</v>
-      </c>
-      <c r="D47" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="G47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" t="s">
         <v>159</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C48" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="G48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" t="s">
         <v>162</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C49" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" t="s">
-        <v>63</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="G49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" t="s">
         <v>165</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C50" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" t="s">
         <v>168</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C51" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="G51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" t="s">
         <v>171</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C52" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="G52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" t="s">
         <v>174</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C53" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" t="s">
-        <v>63</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="G53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
+        <v>176</v>
+      </c>
+      <c r="B54" t="s">
         <v>177</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C54" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" t="s">
         <v>180</v>
-      </c>
-      <c r="B55" t="s">
-        <v>181</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -2794,8 +3150,8 @@
       <c r="D55" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>182</v>
+      <c r="E55" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="G55" t="s">
         <v>35</v>
@@ -2803,70 +3159,70 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" t="s">
         <v>183</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C56" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="G56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" t="s">
         <v>186</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C57" t="s">
-        <v>28</v>
-      </c>
-      <c r="D57" t="s">
-        <v>63</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="G57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
+        <v>188</v>
+      </c>
+      <c r="B58" t="s">
         <v>189</v>
       </c>
-      <c r="B58" t="s">
-        <v>190</v>
-      </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>191</v>
+      <c r="E58" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="G58" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" t="s">
         <v>192</v>
-      </c>
-      <c r="B59" t="s">
-        <v>193</v>
       </c>
       <c r="C59" t="s">
         <v>33</v>
@@ -2874,61 +3230,797 @@
       <c r="D59" t="s">
         <v>11</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>194</v>
+      <c r="E59" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="G59" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="60" customFormat="1" spans="1:7">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" t="s">
         <v>195</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" t="s">
         <v>196</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>197</v>
       </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="G60" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
         <v>198</v>
       </c>
-      <c r="G60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:7">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>199</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" t="s">
         <v>200</v>
       </c>
-      <c r="C61" t="s">
-        <v>197</v>
-      </c>
-      <c r="D61" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="G61" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
         <v>201</v>
       </c>
-      <c r="G61" t="s">
-        <v>8</v>
+      <c r="B62" t="s">
+        <v>202</v>
+      </c>
+      <c r="C62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" t="s">
+        <v>196</v>
+      </c>
+      <c r="E62" t="s">
+        <v>203</v>
+      </c>
+      <c r="G62" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>204</v>
+      </c>
+      <c r="B63" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s">
+        <v>196</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
+      </c>
+      <c r="G63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>207</v>
+      </c>
+      <c r="B64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" t="s">
+        <v>196</v>
+      </c>
+      <c r="E64" t="s">
+        <v>209</v>
+      </c>
+      <c r="G64" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>210</v>
+      </c>
+      <c r="B65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C65" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" t="s">
+        <v>196</v>
+      </c>
+      <c r="E65" t="s">
+        <v>212</v>
+      </c>
+      <c r="G65" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66" t="s">
+        <v>196</v>
+      </c>
+      <c r="E66" t="s">
+        <v>215</v>
+      </c>
+      <c r="G66" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C67" t="s">
+        <v>218</v>
+      </c>
+      <c r="D67" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" t="s">
+        <v>219</v>
+      </c>
+      <c r="G67" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>220</v>
+      </c>
+      <c r="B68" t="s">
+        <v>221</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" t="s">
+        <v>222</v>
+      </c>
+      <c r="G68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>223</v>
+      </c>
+      <c r="B69" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" t="s">
+        <v>225</v>
+      </c>
+      <c r="G69" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" t="s">
+        <v>227</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" t="s">
+        <v>228</v>
+      </c>
+      <c r="G70" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>229</v>
+      </c>
+      <c r="B71" t="s">
+        <v>230</v>
+      </c>
+      <c r="C71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" t="s">
+        <v>196</v>
+      </c>
+      <c r="E71" t="s">
+        <v>231</v>
+      </c>
+      <c r="G71" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>232</v>
+      </c>
+      <c r="B72" t="s">
+        <v>233</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>196</v>
+      </c>
+      <c r="E72" t="s">
+        <v>234</v>
+      </c>
+      <c r="G72" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>235</v>
+      </c>
+      <c r="B73" t="s">
+        <v>236</v>
+      </c>
+      <c r="C73" t="s">
+        <v>237</v>
+      </c>
+      <c r="D73" t="s">
+        <v>196</v>
+      </c>
+      <c r="E73" t="s">
+        <v>238</v>
+      </c>
+      <c r="G73" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>239</v>
+      </c>
+      <c r="B74" t="s">
+        <v>240</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" t="s">
+        <v>241</v>
+      </c>
+      <c r="G74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>242</v>
+      </c>
+      <c r="B75" t="s">
+        <v>243</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" t="s">
+        <v>244</v>
+      </c>
+      <c r="G75" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>245</v>
+      </c>
+      <c r="B76" t="s">
+        <v>246</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" t="s">
+        <v>196</v>
+      </c>
+      <c r="E76" t="s">
+        <v>248</v>
+      </c>
+      <c r="G76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>249</v>
+      </c>
+      <c r="B77" t="s">
+        <v>250</v>
+      </c>
+      <c r="C77" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" t="s">
+        <v>196</v>
+      </c>
+      <c r="E77" t="s">
+        <v>251</v>
+      </c>
+      <c r="G77" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>252</v>
+      </c>
+      <c r="B78" t="s">
+        <v>253</v>
+      </c>
+      <c r="C78" t="s">
+        <v>61</v>
+      </c>
+      <c r="D78" t="s">
+        <v>196</v>
+      </c>
+      <c r="E78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>255</v>
+      </c>
+      <c r="B79" t="s">
+        <v>256</v>
+      </c>
+      <c r="C79" t="s">
+        <v>218</v>
+      </c>
+      <c r="D79" t="s">
+        <v>196</v>
+      </c>
+      <c r="E79" t="s">
+        <v>257</v>
+      </c>
+      <c r="G79" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>258</v>
+      </c>
+      <c r="B80" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" t="s">
+        <v>196</v>
+      </c>
+      <c r="E80" t="s">
+        <v>260</v>
+      </c>
+      <c r="G80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>261</v>
+      </c>
+      <c r="B81" t="s">
+        <v>262</v>
+      </c>
+      <c r="C81" t="s">
+        <v>237</v>
+      </c>
+      <c r="D81" t="s">
+        <v>196</v>
+      </c>
+      <c r="E81" t="s">
+        <v>263</v>
+      </c>
+      <c r="G81" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>264</v>
+      </c>
+      <c r="B82" t="s">
+        <v>265</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s">
+        <v>196</v>
+      </c>
+      <c r="E82" t="s">
+        <v>266</v>
+      </c>
+      <c r="G82" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>267</v>
+      </c>
+      <c r="B83" t="s">
+        <v>268</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
+        <v>196</v>
+      </c>
+      <c r="E83" t="s">
+        <v>269</v>
+      </c>
+      <c r="G83" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>270</v>
+      </c>
+      <c r="B84" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s">
+        <v>218</v>
+      </c>
+      <c r="D84" t="s">
+        <v>196</v>
+      </c>
+      <c r="E84" t="s">
+        <v>272</v>
+      </c>
+      <c r="G84" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>273</v>
+      </c>
+      <c r="B85" t="s">
+        <v>274</v>
+      </c>
+      <c r="C85" t="s">
+        <v>61</v>
+      </c>
+      <c r="D85" t="s">
+        <v>196</v>
+      </c>
+      <c r="E85" t="s">
+        <v>275</v>
+      </c>
+      <c r="G85" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>276</v>
+      </c>
+      <c r="B86" t="s">
+        <v>277</v>
+      </c>
+      <c r="C86" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" t="s">
+        <v>196</v>
+      </c>
+      <c r="E86" t="s">
+        <v>278</v>
+      </c>
+      <c r="G86" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>279</v>
+      </c>
+      <c r="B87" t="s">
+        <v>280</v>
+      </c>
+      <c r="C87" t="s">
+        <v>28</v>
+      </c>
+      <c r="D87" t="s">
+        <v>196</v>
+      </c>
+      <c r="E87" t="s">
+        <v>281</v>
+      </c>
+      <c r="G87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>282</v>
+      </c>
+      <c r="B88" t="s">
+        <v>283</v>
+      </c>
+      <c r="C88" t="s">
+        <v>218</v>
+      </c>
+      <c r="D88" t="s">
+        <v>196</v>
+      </c>
+      <c r="E88" t="s">
+        <v>284</v>
+      </c>
+      <c r="G88" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>285</v>
+      </c>
+      <c r="B89" t="s">
+        <v>286</v>
+      </c>
+      <c r="C89" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" t="s">
+        <v>196</v>
+      </c>
+      <c r="E89" t="s">
+        <v>287</v>
+      </c>
+      <c r="G89" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>288</v>
+      </c>
+      <c r="B90" t="s">
+        <v>289</v>
+      </c>
+      <c r="C90" t="s">
+        <v>218</v>
+      </c>
+      <c r="D90" t="s">
+        <v>196</v>
+      </c>
+      <c r="E90" t="s">
+        <v>290</v>
+      </c>
+      <c r="G90" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>291</v>
+      </c>
+      <c r="B91" t="s">
+        <v>292</v>
+      </c>
+      <c r="C91" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" t="s">
+        <v>196</v>
+      </c>
+      <c r="E91" t="s">
+        <v>293</v>
+      </c>
+      <c r="G91" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>294</v>
+      </c>
+      <c r="B92" t="s">
+        <v>295</v>
+      </c>
+      <c r="C92" t="s">
+        <v>218</v>
+      </c>
+      <c r="D92" t="s">
+        <v>196</v>
+      </c>
+      <c r="E92" t="s">
+        <v>296</v>
+      </c>
+      <c r="G92" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>297</v>
+      </c>
+      <c r="B93" t="s">
+        <v>298</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93" t="s">
+        <v>299</v>
+      </c>
+      <c r="G93" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>300</v>
+      </c>
+      <c r="B94" t="s">
+        <v>301</v>
+      </c>
+      <c r="C94" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" t="s">
+        <v>196</v>
+      </c>
+      <c r="E94" t="s">
+        <v>302</v>
+      </c>
+      <c r="G94" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>303</v>
+      </c>
+      <c r="B95" t="s">
+        <v>304</v>
+      </c>
+      <c r="C95" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" t="s">
+        <v>196</v>
+      </c>
+      <c r="E95" t="s">
+        <v>305</v>
+      </c>
+      <c r="G95" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>306</v>
+      </c>
+      <c r="B96" t="s">
+        <v>307</v>
+      </c>
+      <c r="C96" t="s">
+        <v>33</v>
+      </c>
+      <c r="D96" t="s">
+        <v>196</v>
+      </c>
+      <c r="E96" t="s">
+        <v>308</v>
+      </c>
+      <c r="G96" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>309</v>
+      </c>
+      <c r="B97" t="s">
+        <v>310</v>
+      </c>
+      <c r="C97" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" t="s">
+        <v>196</v>
+      </c>
+      <c r="E97" t="s">
+        <v>311</v>
+      </c>
+      <c r="G97" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>312</v>
+      </c>
+      <c r="B98" t="s">
+        <v>313</v>
+      </c>
+      <c r="C98" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" t="s">
+        <v>196</v>
+      </c>
+      <c r="E98" t="s">
+        <v>314</v>
+      </c>
+      <c r="G98" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H59" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H98" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <hyperlinks>
-    <hyperlink ref="E60" r:id="rId1" display="TienTTT14@fpt.com"/>
-    <hyperlink ref="E61" r:id="rId2" display="NgocHT30@fpt.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
@@ -2940,33 +4032,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.8" customWidth="1"/>
-    <col min="2" max="2" width="25.8" customWidth="1"/>
+    <col min="2" max="2" width="55.75" customWidth="1"/>
     <col min="3" max="3" width="20.8" customWidth="1"/>
     <col min="4" max="6" width="15.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>202</v>
+        <v>315</v>
       </c>
       <c r="B1" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="C1" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="D1" t="s">
-        <v>205</v>
+        <v>318</v>
       </c>
       <c r="E1" t="s">
-        <v>206</v>
+        <v>319</v>
       </c>
       <c r="F1" t="s">
-        <v>207</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2974,891 +4066,1392 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="C2" t="str">
         <f>+VLOOKUP(A2,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F2" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C3" t="str">
         <f>+VLOOKUP(A3,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Phó phòng</v>
+        <v>PM</v>
       </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C4" t="str">
         <f>+VLOOKUP(A4,'Nhân sự'!$A:$C,3,0)</f>
-        <v>PM</v>
+        <v>QC Lead</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C5" t="str">
         <f>+VLOOKUP(A5,'Nhân sự'!$A:$C,3,0)</f>
-        <v>QC Lead</v>
+        <v>Dev</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C6" t="str">
         <f>+VLOOKUP(A6,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>BA</v>
       </c>
       <c r="F6" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C7" t="str">
         <f>+VLOOKUP(A7,'Nhân sự'!$A:$C,3,0)</f>
-        <v>BA</v>
+        <v>Dev Lead</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C8" t="str">
         <f>+VLOOKUP(A8,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tech Lead</v>
+        <v>Dev</v>
       </c>
       <c r="F8" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C9" t="str">
         <f>+VLOOKUP(A9,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Dev Lead</v>
       </c>
       <c r="F9" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C10" t="str">
         <f>+VLOOKUP(A10,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F10" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C11" t="str">
         <f>+VLOOKUP(A11,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev Lead</v>
+        <v>Dev</v>
       </c>
       <c r="F11" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C12" t="str">
         <f>+VLOOKUP(A12,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F12" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C13" t="str">
         <f>+VLOOKUP(A13,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F13" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C14" t="str">
         <f>+VLOOKUP(A14,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>BA</v>
       </c>
       <c r="F14" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C15" t="str">
         <f>+VLOOKUP(A15,'Nhân sự'!$A:$C,3,0)</f>
-        <v>BA</v>
+        <v>Tester</v>
       </c>
       <c r="F15" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C16" t="str">
         <f>+VLOOKUP(A16,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F16" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C17" t="str">
         <f>+VLOOKUP(A17,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>BA Lead</v>
       </c>
       <c r="F17" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C18" t="str">
         <f>+VLOOKUP(A18,'Nhân sự'!$A:$C,3,0)</f>
-        <v>BA Lead</v>
+        <v>BA</v>
       </c>
       <c r="F18" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C19" t="str">
         <f>+VLOOKUP(A19,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F19" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C20" t="str">
         <f>+VLOOKUP(A20,'Nhân sự'!$A:$C,3,0)</f>
-        <v>BA</v>
+        <v>Dev</v>
       </c>
       <c r="F20" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C21" t="str">
         <f>+VLOOKUP(A21,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Tester</v>
       </c>
       <c r="F21" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C22" t="str">
         <f>+VLOOKUP(A22,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>Dev</v>
       </c>
       <c r="F22" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C23" t="str">
         <f>+VLOOKUP(A23,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F23" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C24" t="str">
         <f>+VLOOKUP(A24,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F24" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="C25" t="str">
         <f>+VLOOKUP(A25,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Tester</v>
       </c>
       <c r="F25" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>323</v>
       </c>
       <c r="C26" t="str">
         <f>+VLOOKUP(A26,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>PM</v>
       </c>
       <c r="F26" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C27" t="str">
         <f>+VLOOKUP(A27,'Nhân sự'!$A:$C,3,0)</f>
-        <v>PM</v>
+        <v>Dev Lead</v>
       </c>
       <c r="F27" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C28" t="str">
         <f>+VLOOKUP(A28,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev Lead</v>
+        <v>Dev</v>
       </c>
       <c r="F28" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C29" t="str">
         <f>+VLOOKUP(A29,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Dev Lead</v>
       </c>
       <c r="F29" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C30" t="str">
         <f>+VLOOKUP(A30,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F30" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C31" t="str">
         <f>+VLOOKUP(A31,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev Lead</v>
+        <v>Dev</v>
       </c>
       <c r="F31" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C32" t="str">
         <f>+VLOOKUP(A32,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F32" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C33" t="str">
         <f>+VLOOKUP(A33,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Tester</v>
       </c>
       <c r="F33" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C34" t="str">
         <f>+VLOOKUP(A34,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>QC Lead</v>
       </c>
       <c r="F34" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C35" t="str">
         <f>+VLOOKUP(A35,'Nhân sự'!$A:$C,3,0)</f>
-        <v>QC Lead</v>
+        <v>Tester</v>
       </c>
       <c r="F35" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C36" t="str">
         <f>+VLOOKUP(A36,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F36" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C37" t="str">
         <f>+VLOOKUP(A37,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>Dev</v>
       </c>
       <c r="F37" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C38" t="str">
         <f>+VLOOKUP(A38,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F38" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B39" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C39" t="str">
         <f>+VLOOKUP(A39,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F39" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>324</v>
       </c>
       <c r="C40" t="str">
         <f>+VLOOKUP(A40,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>PM</v>
       </c>
       <c r="F40" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C41" t="str">
         <f>+VLOOKUP(A41,'Nhân sự'!$A:$C,3,0)</f>
-        <v>PM</v>
+        <v>BA</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C42" t="str">
         <f>+VLOOKUP(A42,'Nhân sự'!$A:$C,3,0)</f>
-        <v>BA</v>
+        <v>Dev</v>
       </c>
       <c r="F42" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C43" t="str">
         <f>+VLOOKUP(A43,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Dev Lead</v>
       </c>
       <c r="F43" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C44" t="str">
         <f>+VLOOKUP(A44,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev Lead</v>
+        <v>Tester</v>
       </c>
       <c r="F44" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C45" t="str">
         <f>+VLOOKUP(A45,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F45" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C46" t="str">
         <f>+VLOOKUP(A46,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F46" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C47" t="str">
         <f>+VLOOKUP(A47,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F47" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C48" t="str">
         <f>+VLOOKUP(A48,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F48" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B49" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C49" t="str">
         <f>+VLOOKUP(A49,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F49" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B50" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C50" t="str">
         <f>+VLOOKUP(A50,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F50" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C51" t="str">
         <f>+VLOOKUP(A51,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>Dev</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C52" t="str">
         <f>+VLOOKUP(A52,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F52" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="C53" t="str">
         <f>+VLOOKUP(A53,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="C54" t="str">
         <f>+VLOOKUP(A54,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F54" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
-        <v>212</v>
+        <v>326</v>
       </c>
       <c r="C55" t="str">
         <f>+VLOOKUP(A55,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>Tester</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
-        <v>213</v>
+        <v>326</v>
       </c>
       <c r="C56" t="str">
         <f>+VLOOKUP(A56,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Tester</v>
+        <v>Dev</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C57" t="str">
         <f>+VLOOKUP(A57,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Dev</v>
+        <v>BA</v>
       </c>
       <c r="F57" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="B58" t="s">
-        <v>213</v>
-      </c>
-      <c r="C58" t="str">
-        <f>+VLOOKUP(A58,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Phó phòng</v>
+        <v>328</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C59" t="str">
-        <f>+VLOOKUP(A59,'Nhân sự'!$A:$C,3,0)</f>
-        <v>BA</v>
+        <v>329</v>
+      </c>
+      <c r="C59" t="s">
+        <v>33</v>
       </c>
       <c r="F59" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:6">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>201</v>
       </c>
       <c r="B60" t="s">
-        <v>211</v>
-      </c>
-      <c r="C60" t="str">
-        <f>+VLOOKUP(A60,'Nhân sự'!$A:$C,3,0)</f>
-        <v>Phó phòng</v>
+        <v>328</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
       </c>
       <c r="F60" t="s">
-        <v>209</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>204</v>
+      </c>
+      <c r="B61" t="s">
+        <v>328</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="F61" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>207</v>
+      </c>
+      <c r="B62" t="s">
+        <v>328</v>
+      </c>
+      <c r="C62" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>210</v>
+      </c>
+      <c r="B63" t="s">
+        <v>328</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" t="s">
+        <v>329</v>
+      </c>
+      <c r="C64" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B65" t="s">
+        <v>329</v>
+      </c>
+      <c r="C65" t="s">
+        <v>218</v>
+      </c>
+      <c r="F65" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>220</v>
+      </c>
+      <c r="B66" t="s">
+        <v>328</v>
+      </c>
+      <c r="C66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>229</v>
+      </c>
+      <c r="B69" t="s">
+        <v>330</v>
+      </c>
+      <c r="C69" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>232</v>
+      </c>
+      <c r="B70" t="s">
+        <v>330</v>
+      </c>
+      <c r="C70" t="s">
+        <v>28</v>
+      </c>
+      <c r="F70" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>235</v>
+      </c>
+      <c r="B71" t="s">
+        <v>328</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="F71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>239</v>
+      </c>
+      <c r="B72" t="s">
+        <v>330</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" t="s">
+        <v>330</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>245</v>
+      </c>
+      <c r="B74" t="s">
+        <v>329</v>
+      </c>
+      <c r="C74" t="s">
+        <v>247</v>
+      </c>
+      <c r="F74" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" t="s">
+        <v>329</v>
+      </c>
+      <c r="C75" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>252</v>
+      </c>
+      <c r="B76" t="s">
+        <v>328</v>
+      </c>
+      <c r="C76" t="s">
+        <v>61</v>
+      </c>
+      <c r="F76" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>255</v>
+      </c>
+      <c r="B77" t="s">
+        <v>324</v>
+      </c>
+      <c r="C77" t="s">
+        <v>218</v>
+      </c>
+      <c r="F77" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" t="s">
+        <v>331</v>
+      </c>
+      <c r="C78" t="s">
+        <v>33</v>
+      </c>
+      <c r="F78" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>261</v>
+      </c>
+      <c r="B79" t="s">
+        <v>328</v>
+      </c>
+      <c r="C79" t="s">
+        <v>237</v>
+      </c>
+      <c r="F79" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>264</v>
+      </c>
+      <c r="B80" t="s">
+        <v>329</v>
+      </c>
+      <c r="C80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>267</v>
+      </c>
+      <c r="B81" t="s">
+        <v>329</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>270</v>
+      </c>
+      <c r="B82" t="s">
+        <v>329</v>
+      </c>
+      <c r="C82" t="s">
+        <v>218</v>
+      </c>
+      <c r="F82" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>273</v>
+      </c>
+      <c r="B83" t="s">
+        <v>329</v>
+      </c>
+      <c r="C83" t="s">
+        <v>61</v>
+      </c>
+      <c r="F83" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>276</v>
+      </c>
+      <c r="B84" t="s">
+        <v>329</v>
+      </c>
+      <c r="C84" t="s">
+        <v>33</v>
+      </c>
+      <c r="F84" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>279</v>
+      </c>
+      <c r="B85" t="s">
+        <v>328</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>282</v>
+      </c>
+      <c r="B86" t="s">
+        <v>321</v>
+      </c>
+      <c r="C86" t="s">
+        <v>218</v>
+      </c>
+      <c r="F86" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>285</v>
+      </c>
+      <c r="B87" t="s">
+        <v>329</v>
+      </c>
+      <c r="C87" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>288</v>
+      </c>
+      <c r="B88" t="s">
+        <v>321</v>
+      </c>
+      <c r="C88" t="s">
+        <v>218</v>
+      </c>
+      <c r="F88" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" t="s">
+        <v>321</v>
+      </c>
+      <c r="C89" t="s">
+        <v>218</v>
+      </c>
+      <c r="F89" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" t="s">
+        <v>321</v>
+      </c>
+      <c r="C90" t="s">
+        <v>218</v>
+      </c>
+      <c r="F90" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>297</v>
+      </c>
+      <c r="B91" t="s">
+        <v>332</v>
+      </c>
+      <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="F91" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>300</v>
+      </c>
+      <c r="B92" t="s">
+        <v>328</v>
+      </c>
+      <c r="C92" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>303</v>
+      </c>
+      <c r="B93" t="s">
+        <v>329</v>
+      </c>
+      <c r="C93" t="s">
+        <v>33</v>
+      </c>
+      <c r="F93" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>306</v>
+      </c>
+      <c r="B94" t="s">
+        <v>321</v>
+      </c>
+      <c r="C94" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>309</v>
+      </c>
+      <c r="B95" t="s">
+        <v>333</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="F95" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>312</v>
+      </c>
+      <c r="B96" t="s">
+        <v>330</v>
+      </c>
+      <c r="C96" t="s">
+        <v>28</v>
+      </c>
+      <c r="F96" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="F2 A1:F1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/data/sample-data-55emp-6proj.xlsx
+++ b/src/assets/data/sample-data-55emp-6proj.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="10860" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="Nhân sự" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="340">
   <si>
     <t>ID</t>
   </si>
@@ -978,6 +978,27 @@
     <t>PhungNT15@fpt.com</t>
   </si>
   <si>
+    <t>NV098</t>
+  </si>
+  <si>
+    <t>Trần Thụy Thủy Tiên</t>
+  </si>
+  <si>
+    <t>PMO</t>
+  </si>
+  <si>
+    <t>TienTTT14@fpt.com</t>
+  </si>
+  <si>
+    <t>NV099</t>
+  </si>
+  <si>
+    <t>Hà Thúy Ngọc</t>
+  </si>
+  <si>
+    <t>NgocHT3@fpt.com</t>
+  </si>
+  <si>
     <t>ID nhân viên</t>
   </si>
   <si>
@@ -1030,9 +1051,6 @@
   </si>
   <si>
     <t>Project liên quan Akabot</t>
-  </si>
-  <si>
-    <t>Chưa vào ạ</t>
   </si>
 </sst>
 </file>
@@ -1054,18 +1072,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1508,28 +1526,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1653,8 +1671,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2039,7 +2058,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.8" customWidth="1"/>
@@ -2090,7 +2109,7 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G2" t="s">
@@ -2110,7 +2129,7 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
@@ -2130,7 +2149,7 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G4" t="s">
@@ -2150,7 +2169,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G5" t="s">
@@ -2170,7 +2189,7 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G6" t="s">
@@ -2190,7 +2209,7 @@
       <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G7" t="s">
@@ -2210,7 +2229,7 @@
       <c r="D8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G8" t="s">
@@ -2230,7 +2249,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G9" t="s">
@@ -2250,7 +2269,7 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G10" t="s">
@@ -2270,7 +2289,7 @@
       <c r="D11" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G11" t="s">
@@ -2290,7 +2309,7 @@
       <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G12" t="s">
@@ -2310,7 +2329,7 @@
       <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G13" t="s">
@@ -2330,7 +2349,7 @@
       <c r="D14" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G14" t="s">
@@ -2350,7 +2369,7 @@
       <c r="D15" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>58</v>
       </c>
       <c r="G15" t="s">
@@ -2370,7 +2389,7 @@
       <c r="D16" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G16" t="s">
@@ -2390,7 +2409,7 @@
       <c r="D17" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G17" t="s">
@@ -2410,7 +2429,7 @@
       <c r="D18" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" t="s">
@@ -2430,7 +2449,7 @@
       <c r="D19" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>73</v>
       </c>
       <c r="G19" t="s">
@@ -2450,7 +2469,7 @@
       <c r="D20" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G20" t="s">
@@ -2470,7 +2489,7 @@
       <c r="D21" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G21" t="s">
@@ -2490,7 +2509,7 @@
       <c r="D22" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G22" t="s">
@@ -2510,7 +2529,7 @@
       <c r="D23" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>85</v>
       </c>
       <c r="G23" t="s">
@@ -2530,7 +2549,7 @@
       <c r="D24" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G24" t="s">
@@ -2550,7 +2569,7 @@
       <c r="D25" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G25" t="s">
@@ -2570,7 +2589,7 @@
       <c r="D26" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G26" t="s">
@@ -2590,7 +2609,7 @@
       <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>97</v>
       </c>
       <c r="G27" t="s">
@@ -2610,7 +2629,7 @@
       <c r="D28" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G28" t="s">
@@ -2630,7 +2649,7 @@
       <c r="D29" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>103</v>
       </c>
       <c r="G29" t="s">
@@ -2650,7 +2669,7 @@
       <c r="D30" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>106</v>
       </c>
       <c r="G30" t="s">
@@ -2670,7 +2689,7 @@
       <c r="D31" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>109</v>
       </c>
       <c r="G31" t="s">
@@ -2690,7 +2709,7 @@
       <c r="D32" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>112</v>
       </c>
       <c r="G32" t="s">
@@ -2710,7 +2729,7 @@
       <c r="D33" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>115</v>
       </c>
       <c r="G33" t="s">
@@ -2730,7 +2749,7 @@
       <c r="D34" t="s">
         <v>62</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>118</v>
       </c>
       <c r="G34" t="s">
@@ -2750,7 +2769,7 @@
       <c r="D35" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>121</v>
       </c>
       <c r="G35" t="s">
@@ -2770,7 +2789,7 @@
       <c r="D36" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>124</v>
       </c>
       <c r="G36" t="s">
@@ -2790,7 +2809,7 @@
       <c r="D37" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>127</v>
       </c>
       <c r="G37" t="s">
@@ -2810,7 +2829,7 @@
       <c r="D38" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>130</v>
       </c>
       <c r="G38" t="s">
@@ -2830,7 +2849,7 @@
       <c r="D39" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>133</v>
       </c>
       <c r="G39" t="s">
@@ -2850,7 +2869,7 @@
       <c r="D40" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>136</v>
       </c>
       <c r="G40" t="s">
@@ -2870,7 +2889,7 @@
       <c r="D41" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>139</v>
       </c>
       <c r="G41" t="s">
@@ -2890,7 +2909,7 @@
       <c r="D42" t="s">
         <v>11</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>142</v>
       </c>
       <c r="G42" t="s">
@@ -2910,7 +2929,7 @@
       <c r="D43" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>145</v>
       </c>
       <c r="G43" t="s">
@@ -2930,7 +2949,7 @@
       <c r="D44" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>148</v>
       </c>
       <c r="G44" t="s">
@@ -2950,7 +2969,7 @@
       <c r="D45" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>151</v>
       </c>
       <c r="G45" t="s">
@@ -2970,7 +2989,7 @@
       <c r="D46" t="s">
         <v>62</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>154</v>
       </c>
       <c r="G46" t="s">
@@ -2990,7 +3009,7 @@
       <c r="D47" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>157</v>
       </c>
       <c r="G47" t="s">
@@ -3010,7 +3029,7 @@
       <c r="D48" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>160</v>
       </c>
       <c r="G48" t="s">
@@ -3030,7 +3049,7 @@
       <c r="D49" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>163</v>
       </c>
       <c r="G49" t="s">
@@ -3050,7 +3069,7 @@
       <c r="D50" t="s">
         <v>62</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>166</v>
       </c>
       <c r="G50" t="s">
@@ -3070,7 +3089,7 @@
       <c r="D51" t="s">
         <v>62</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G51" t="s">
@@ -3090,7 +3109,7 @@
       <c r="D52" t="s">
         <v>62</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="2" t="s">
         <v>172</v>
       </c>
       <c r="G52" t="s">
@@ -3110,7 +3129,7 @@
       <c r="D53" t="s">
         <v>62</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G53" t="s">
@@ -3130,7 +3149,7 @@
       <c r="D54" t="s">
         <v>62</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="2" t="s">
         <v>178</v>
       </c>
       <c r="G54" t="s">
@@ -3150,7 +3169,7 @@
       <c r="D55" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="2" t="s">
         <v>181</v>
       </c>
       <c r="G55" t="s">
@@ -3170,7 +3189,7 @@
       <c r="D56" t="s">
         <v>62</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="2" t="s">
         <v>184</v>
       </c>
       <c r="G56" t="s">
@@ -3190,7 +3209,7 @@
       <c r="D57" t="s">
         <v>62</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="2" t="s">
         <v>187</v>
       </c>
       <c r="G57" t="s">
@@ -3210,7 +3229,7 @@
       <c r="D58" t="s">
         <v>11</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="2" t="s">
         <v>190</v>
       </c>
       <c r="G58" t="s">
@@ -3230,7 +3249,7 @@
       <c r="D59" t="s">
         <v>11</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="2" t="s">
         <v>193</v>
       </c>
       <c r="G59" t="s">
@@ -4015,16 +4034,60 @@
       </c>
       <c r="G98" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>315</v>
+      </c>
+      <c r="B99" t="s">
+        <v>316</v>
+      </c>
+      <c r="C99" t="s">
+        <v>317</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>319</v>
+      </c>
+      <c r="B100" t="s">
+        <v>320</v>
+      </c>
+      <c r="C100" t="s">
+        <v>317</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G100" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H98" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="E99" r:id="rId1" display="TienTTT14@fpt.com"/>
+    <hyperlink ref="E100" r:id="rId2" display="NgocHT3@fpt.com" tooltip="mailto:NgocHT3@fpt.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="G2:G3 F1:H1 A1:D1 A2" numberStoredAsText="1"/>
+    <ignoredError sqref="A2 A1:D1 F1:H1 G2:G3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4032,7 +4095,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.8" customWidth="1"/>
@@ -4043,22 +4106,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E1" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F1" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4066,14 +4129,14 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C2" t="str">
         <f>+VLOOKUP(A2,'Nhân sự'!$A:$C,3,0)</f>
         <v>Phó phòng</v>
       </c>
       <c r="F2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4081,14 +4144,14 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C3" t="str">
         <f>+VLOOKUP(A3,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4096,14 +4159,14 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C4" t="str">
         <f>+VLOOKUP(A4,'Nhân sự'!$A:$C,3,0)</f>
         <v>QC Lead</v>
       </c>
       <c r="F4" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4111,14 +4174,14 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C5" t="str">
         <f>+VLOOKUP(A5,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4126,14 +4189,14 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C6" t="str">
         <f>+VLOOKUP(A6,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F6" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4141,14 +4204,14 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C7" t="str">
         <f>+VLOOKUP(A7,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F7" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4156,14 +4219,14 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C8" t="str">
         <f>+VLOOKUP(A8,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F8" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4171,14 +4234,14 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C9" t="str">
         <f>+VLOOKUP(A9,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F9" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4186,14 +4249,14 @@
         <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C10" t="str">
         <f>+VLOOKUP(A10,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F10" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4201,14 +4264,14 @@
         <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C11" t="str">
         <f>+VLOOKUP(A11,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F11" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4216,14 +4279,14 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C12" t="str">
         <f>+VLOOKUP(A12,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F12" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4231,14 +4294,14 @@
         <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C13" t="str">
         <f>+VLOOKUP(A13,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F13" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4246,14 +4309,14 @@
         <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C14" t="str">
         <f>+VLOOKUP(A14,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F14" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4261,14 +4324,14 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C15" t="str">
         <f>+VLOOKUP(A15,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F15" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4276,14 +4339,14 @@
         <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C16" t="str">
         <f>+VLOOKUP(A16,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F16" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4291,14 +4354,14 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C17" t="str">
         <f>+VLOOKUP(A17,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA Lead</v>
       </c>
       <c r="F17" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4306,14 +4369,14 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C18" t="str">
         <f>+VLOOKUP(A18,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F18" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4321,14 +4384,14 @@
         <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C19" t="str">
         <f>+VLOOKUP(A19,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F19" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4336,14 +4399,14 @@
         <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C20" t="str">
         <f>+VLOOKUP(A20,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F20" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4351,14 +4414,14 @@
         <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C21" t="str">
         <f>+VLOOKUP(A21,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F21" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4366,14 +4429,14 @@
         <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C22" t="str">
         <f>+VLOOKUP(A22,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F22" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4381,14 +4444,14 @@
         <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C23" t="str">
         <f>+VLOOKUP(A23,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F23" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4396,14 +4459,14 @@
         <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C24" t="str">
         <f>+VLOOKUP(A24,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F24" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4411,14 +4474,14 @@
         <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C25" t="str">
         <f>+VLOOKUP(A25,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F25" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4426,14 +4489,14 @@
         <v>95</v>
       </c>
       <c r="B26" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C26" t="str">
         <f>+VLOOKUP(A26,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F26" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4441,14 +4504,14 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C27" t="str">
         <f>+VLOOKUP(A27,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F27" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4456,14 +4519,14 @@
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C28" t="str">
         <f>+VLOOKUP(A28,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F28" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4471,14 +4534,14 @@
         <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C29" t="str">
         <f>+VLOOKUP(A29,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F29" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4486,14 +4549,14 @@
         <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C30" t="str">
         <f>+VLOOKUP(A30,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F30" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4501,14 +4564,14 @@
         <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C31" t="str">
         <f>+VLOOKUP(A31,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F31" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4516,14 +4579,14 @@
         <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C32" t="str">
         <f>+VLOOKUP(A32,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F32" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4531,14 +4594,14 @@
         <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C33" t="str">
         <f>+VLOOKUP(A33,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F33" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4546,14 +4609,14 @@
         <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C34" t="str">
         <f>+VLOOKUP(A34,'Nhân sự'!$A:$C,3,0)</f>
         <v>QC Lead</v>
       </c>
       <c r="F34" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4561,14 +4624,14 @@
         <v>122</v>
       </c>
       <c r="B35" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C35" t="str">
         <f>+VLOOKUP(A35,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F35" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4576,14 +4639,14 @@
         <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C36" t="str">
         <f>+VLOOKUP(A36,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F36" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4591,14 +4654,14 @@
         <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C37" t="str">
         <f>+VLOOKUP(A37,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F37" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4606,14 +4669,14 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C38" t="str">
         <f>+VLOOKUP(A38,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F38" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4621,14 +4684,14 @@
         <v>134</v>
       </c>
       <c r="B39" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C39" t="str">
         <f>+VLOOKUP(A39,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F39" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4636,14 +4699,14 @@
         <v>137</v>
       </c>
       <c r="B40" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C40" t="str">
         <f>+VLOOKUP(A40,'Nhân sự'!$A:$C,3,0)</f>
         <v>PM</v>
       </c>
       <c r="F40" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4651,14 +4714,14 @@
         <v>140</v>
       </c>
       <c r="B41" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C41" t="str">
         <f>+VLOOKUP(A41,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F41" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4666,14 +4729,14 @@
         <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C42" t="str">
         <f>+VLOOKUP(A42,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F42" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4681,14 +4744,14 @@
         <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C43" t="str">
         <f>+VLOOKUP(A43,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev Lead</v>
       </c>
       <c r="F43" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4696,14 +4759,14 @@
         <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C44" t="str">
         <f>+VLOOKUP(A44,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F44" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4711,14 +4774,14 @@
         <v>152</v>
       </c>
       <c r="B45" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C45" t="str">
         <f>+VLOOKUP(A45,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F45" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4726,14 +4789,14 @@
         <v>155</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C46" t="str">
         <f>+VLOOKUP(A46,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F46" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4741,14 +4804,14 @@
         <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C47" t="str">
         <f>+VLOOKUP(A47,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F47" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4756,14 +4819,14 @@
         <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C48" t="str">
         <f>+VLOOKUP(A48,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F48" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4771,14 +4834,14 @@
         <v>164</v>
       </c>
       <c r="B49" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C49" t="str">
         <f>+VLOOKUP(A49,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F49" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4786,14 +4849,14 @@
         <v>167</v>
       </c>
       <c r="B50" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C50" t="str">
         <f>+VLOOKUP(A50,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F50" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4801,14 +4864,14 @@
         <v>170</v>
       </c>
       <c r="B51" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C51" t="str">
         <f>+VLOOKUP(A51,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F51" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4816,14 +4879,14 @@
         <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C52" t="str">
         <f>+VLOOKUP(A52,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F52" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4831,14 +4894,14 @@
         <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C53" t="str">
         <f>+VLOOKUP(A53,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F53" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4846,14 +4909,14 @@
         <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C54" t="str">
         <f>+VLOOKUP(A54,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F54" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4861,14 +4924,14 @@
         <v>182</v>
       </c>
       <c r="B55" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C55" t="str">
         <f>+VLOOKUP(A55,'Nhân sự'!$A:$C,3,0)</f>
         <v>Tester</v>
       </c>
       <c r="F55" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4876,14 +4939,14 @@
         <v>185</v>
       </c>
       <c r="B56" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C56" t="str">
         <f>+VLOOKUP(A56,'Nhân sự'!$A:$C,3,0)</f>
         <v>Dev</v>
       </c>
       <c r="F56" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4891,14 +4954,14 @@
         <v>191</v>
       </c>
       <c r="B57" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C57" t="str">
         <f>+VLOOKUP(A57,'Nhân sự'!$A:$C,3,0)</f>
         <v>BA</v>
       </c>
       <c r="F57" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4906,13 +4969,13 @@
         <v>194</v>
       </c>
       <c r="B58" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C58" t="s">
         <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4920,13 +4983,13 @@
         <v>198</v>
       </c>
       <c r="B59" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C59" t="s">
         <v>33</v>
       </c>
       <c r="F59" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4934,13 +4997,13 @@
         <v>201</v>
       </c>
       <c r="B60" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
       </c>
       <c r="F60" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4948,13 +5011,13 @@
         <v>204</v>
       </c>
       <c r="B61" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C61" t="s">
         <v>28</v>
       </c>
       <c r="F61" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -4962,13 +5025,13 @@
         <v>207</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C62" t="s">
         <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -4976,13 +5039,13 @@
         <v>210</v>
       </c>
       <c r="B63" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
       </c>
       <c r="F63" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -4990,13 +5053,13 @@
         <v>213</v>
       </c>
       <c r="B64" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C64" t="s">
         <v>61</v>
       </c>
       <c r="F64" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5004,13 +5067,13 @@
         <v>216</v>
       </c>
       <c r="B65" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C65" t="s">
         <v>218</v>
       </c>
       <c r="F65" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5018,13 +5081,13 @@
         <v>220</v>
       </c>
       <c r="B66" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
       </c>
       <c r="F66" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5032,13 +5095,13 @@
         <v>223</v>
       </c>
       <c r="B67" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
       </c>
       <c r="F67" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5046,13 +5109,13 @@
         <v>226</v>
       </c>
       <c r="B68" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
       </c>
       <c r="F68" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5060,13 +5123,13 @@
         <v>229</v>
       </c>
       <c r="B69" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
       </c>
       <c r="F69" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -5074,13 +5137,13 @@
         <v>232</v>
       </c>
       <c r="B70" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C70" t="s">
         <v>28</v>
       </c>
       <c r="F70" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -5088,13 +5151,13 @@
         <v>235</v>
       </c>
       <c r="B71" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C71" t="s">
         <v>237</v>
       </c>
       <c r="F71" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5102,13 +5165,13 @@
         <v>239</v>
       </c>
       <c r="B72" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C72" t="s">
         <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -5116,13 +5179,13 @@
         <v>242</v>
       </c>
       <c r="B73" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C73" t="s">
         <v>28</v>
       </c>
       <c r="F73" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5130,13 +5193,13 @@
         <v>245</v>
       </c>
       <c r="B74" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C74" t="s">
         <v>247</v>
       </c>
       <c r="F74" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5144,13 +5207,13 @@
         <v>249</v>
       </c>
       <c r="B75" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C75" t="s">
         <v>33</v>
       </c>
       <c r="F75" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5158,13 +5221,13 @@
         <v>252</v>
       </c>
       <c r="B76" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C76" t="s">
         <v>61</v>
       </c>
       <c r="F76" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5172,13 +5235,13 @@
         <v>255</v>
       </c>
       <c r="B77" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C77" t="s">
         <v>218</v>
       </c>
       <c r="F77" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5186,13 +5249,13 @@
         <v>258</v>
       </c>
       <c r="B78" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C78" t="s">
         <v>33</v>
       </c>
       <c r="F78" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5200,13 +5263,13 @@
         <v>261</v>
       </c>
       <c r="B79" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C79" t="s">
         <v>237</v>
       </c>
       <c r="F79" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5214,13 +5277,13 @@
         <v>264</v>
       </c>
       <c r="B80" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C80" t="s">
         <v>28</v>
       </c>
       <c r="F80" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5228,13 +5291,13 @@
         <v>267</v>
       </c>
       <c r="B81" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C81" t="s">
         <v>28</v>
       </c>
       <c r="F81" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5242,13 +5305,13 @@
         <v>270</v>
       </c>
       <c r="B82" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C82" t="s">
         <v>218</v>
       </c>
       <c r="F82" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5256,13 +5319,13 @@
         <v>273</v>
       </c>
       <c r="B83" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C83" t="s">
         <v>61</v>
       </c>
       <c r="F83" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -5270,13 +5333,13 @@
         <v>276</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C84" t="s">
         <v>33</v>
       </c>
       <c r="F84" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5284,13 +5347,13 @@
         <v>279</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C85" t="s">
         <v>28</v>
       </c>
       <c r="F85" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5298,13 +5361,13 @@
         <v>282</v>
       </c>
       <c r="B86" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C86" t="s">
         <v>218</v>
       </c>
       <c r="F86" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5312,13 +5375,13 @@
         <v>285</v>
       </c>
       <c r="B87" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C87" t="s">
         <v>33</v>
       </c>
       <c r="F87" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5326,13 +5389,13 @@
         <v>288</v>
       </c>
       <c r="B88" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C88" t="s">
         <v>218</v>
       </c>
       <c r="F88" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5340,13 +5403,13 @@
         <v>291</v>
       </c>
       <c r="B89" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C89" t="s">
         <v>218</v>
       </c>
       <c r="F89" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5354,13 +5417,13 @@
         <v>294</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C90" t="s">
         <v>218</v>
       </c>
       <c r="F90" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5368,13 +5431,13 @@
         <v>297</v>
       </c>
       <c r="B91" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C91" t="s">
         <v>28</v>
       </c>
       <c r="F91" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -5382,13 +5445,13 @@
         <v>300</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C92" t="s">
         <v>28</v>
       </c>
       <c r="F92" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5396,13 +5459,13 @@
         <v>303</v>
       </c>
       <c r="B93" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C93" t="s">
         <v>33</v>
       </c>
       <c r="F93" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5410,41 +5473,27 @@
         <v>306</v>
       </c>
       <c r="B94" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C94" t="s">
         <v>33</v>
       </c>
       <c r="F94" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B95" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
       </c>
       <c r="F95" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" t="s">
-        <v>312</v>
-      </c>
-      <c r="B96" t="s">
-        <v>330</v>
-      </c>
-      <c r="C96" t="s">
-        <v>28</v>
-      </c>
-      <c r="F96" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
